--- a/main/training_dataset.xlsx
+++ b/main/training_dataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="273">
   <si>
     <t>LLM model</t>
   </si>
@@ -2622,9 +2622,6 @@
   </si>
   <si>
     <t>Average Google offsite WUE</t>
-  </si>
-  <si>
-    <t>Energy type sources</t>
   </si>
   <si>
     <t>US east (Virginia)</t>
@@ -7045,13 +7042,11 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>255</v>
-      </c>
+      <c r="P1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B2" s="2">
         <v>2.385</v>
@@ -7061,13 +7056,13 @@
         <v>7.026833333</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H2" s="2">
         <v>3.1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J2" s="5">
         <f>AVERAGE(H2:H12)</f>
@@ -7076,114 +7071,114 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B3" s="2">
         <v>3.526</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H3" s="2">
         <v>2.04</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B4" s="2">
         <v>9.5</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H4" s="2">
         <v>2.34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B5" s="2">
         <v>3.44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H5" s="2">
         <v>2.23</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B6" s="2">
         <v>4.73</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H6" s="2">
         <v>1.29</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B7" s="2">
         <v>18.58</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H7" s="2">
         <v>9.5</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
       <c r="G8" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H8" s="2">
         <v>4.96</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9">
       <c r="G9" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H9" s="2">
         <v>3.44</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
       <c r="G10" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H10" s="2">
         <v>2.18</v>
@@ -7194,24 +7189,24 @@
     </row>
     <row r="11">
       <c r="G11" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H11" s="2">
         <v>2.31</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
       <c r="G12" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H12" s="2">
         <v>10.5</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
